--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J65-SubjectRole-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J65-SubjectRole-DMP.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2284,18 +2284,6 @@
     <t>Responsable d'établissement</t>
   </si>
   <si>
-    <t>FON-15</t>
-  </si>
-  <si>
-    <t>Directeur de laboratoire</t>
-  </si>
-  <si>
-    <t>FON-16</t>
-  </si>
-  <si>
-    <t>Directeur-adjoint de laboratoire</t>
-  </si>
-  <si>
     <t>FON-17</t>
   </si>
   <si>
@@ -2620,6 +2608,12 @@
     <t>329</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Coordonnateur de parcours</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
@@ -2650,28 +2644,34 @@
     <t>Gestionnaire alertes et urgences sanitaires</t>
   </si>
   <si>
-    <t>350</t>
+    <t>351</t>
+  </si>
+  <si>
+    <t>Assistant(e) maternel(le)</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Autre salarié de la structure sociale</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Membre de l'équipe de soins</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Aide à domicile qualifié(e)</t>
+  </si>
+  <si>
+    <t>372</t>
   </si>
   <si>
     <t>Aide à domicile</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>Assistant(e) maternel(le)</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Autre salarié de la structure sociale</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>Membre de l'équipe de soins</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
@@ -3070,6 +3070,356 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>817</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -3087,330 +3437,330 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>739</v>
+        <v>818</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>740</v>
+        <v>819</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>741</v>
+        <v>820</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>742</v>
+        <v>821</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>743</v>
+        <v>822</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>744</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>745</v>
+        <v>824</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>746</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>747</v>
+        <v>826</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>748</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>749</v>
+        <v>828</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>750</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>751</v>
+        <v>830</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>752</v>
+        <v>831</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>753</v>
+        <v>832</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>754</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>755</v>
+        <v>834</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>756</v>
+        <v>835</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>757</v>
+        <v>836</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>758</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>759</v>
+        <v>838</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>760</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>761</v>
+        <v>840</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>762</v>
+        <v>841</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>763</v>
+        <v>842</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>764</v>
+        <v>843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>765</v>
+        <v>844</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>766</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>767</v>
+        <v>845</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>768</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>769</v>
+        <v>846</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>770</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>771</v>
+        <v>847</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>772</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>773</v>
+        <v>848</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>774</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>775</v>
+        <v>849</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>776</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>777</v>
+        <v>850</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>778</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>779</v>
+        <v>851</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>780</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>781</v>
+        <v>852</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>782</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>783</v>
+        <v>853</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>784</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>785</v>
+        <v>854</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>786</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>787</v>
+        <v>855</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>788</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>789</v>
+        <v>856</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>790</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>791</v>
+        <v>857</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>792</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>793</v>
+        <v>858</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>794</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>795</v>
+        <v>859</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>796</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>797</v>
+        <v>860</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>798</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>799</v>
+        <v>861</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>800</v>
+        <v>862</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>801</v>
+        <v>863</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>802</v>
+        <v>864</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>803</v>
+        <v>865</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>804</v>
+        <v>866</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>805</v>
+        <v>867</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>806</v>
+        <v>868</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>807</v>
+        <v>869</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>808</v>
+        <v>870</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>809</v>
+        <v>871</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>810</v>
+        <v>872</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>811</v>
+        <v>873</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>812</v>
+        <v>874</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>813</v>
+        <v>875</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>814</v>
+        <v>876</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>815</v>
+        <v>877</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>816</v>
+        <v>878</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>817</v>
+        <v>879</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>818</v>
+        <v>880</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>819</v>
+        <v>881</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>820</v>
+        <v>882</v>
       </c>
     </row>
     <row r="43">
@@ -3426,356 +3776,6 @@
         <v>39</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>821</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B42" t="s" s="2">
         <v>883</v>
       </c>
     </row>
